--- a/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_502_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_502_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_502_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_502_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1301,11 +1293,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1313,7 +1301,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1554,11 +1542,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1566,7 +1550,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1807,11 +1791,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1819,7 +1799,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2060,11 +2040,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2072,7 +2048,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2313,11 +2289,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2325,7 +2297,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2566,11 +2538,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2578,7 +2546,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2819,11 +2787,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2831,7 +2795,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3068,11 +3032,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3080,7 +3040,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3321,11 +3281,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3333,7 +3289,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3574,11 +3530,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3586,7 +3538,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3827,11 +3779,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3839,7 +3787,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4080,11 +4028,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4092,7 +4036,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4325,11 +4269,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4337,7 +4277,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4570,11 +4510,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4582,7 +4518,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4823,11 +4759,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4835,7 +4767,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5076,11 +5008,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5088,7 +5016,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5325,11 +5253,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5337,7 +5261,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5578,11 +5502,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5590,7 +5510,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5827,11 +5747,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5839,7 +5755,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6072,11 +5988,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6084,7 +5996,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6325,11 +6237,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6337,7 +6245,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6578,11 +6486,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6590,7 +6494,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6831,11 +6735,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6843,7 +6743,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7084,11 +6984,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7096,7 +6992,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7329,11 +7225,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7341,7 +7233,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7582,11 +7474,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7594,7 +7482,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7835,11 +7723,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7847,7 +7731,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8076,11 +7960,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8088,7 +7968,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8285,11 +8165,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8297,7 +8173,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8538,11 +8414,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8550,7 +8422,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8791,11 +8663,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8803,7 +8671,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9044,11 +8912,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9056,7 +8920,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9297,11 +9161,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9309,7 +9169,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9550,11 +9410,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9562,7 +9418,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9791,11 +9647,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9803,7 +9655,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10044,11 +9896,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -10056,7 +9904,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10297,11 +10145,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -10309,7 +10153,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10550,11 +10394,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -10562,7 +10402,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10803,11 +10643,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -10815,7 +10651,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11056,11 +10892,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -11068,7 +10900,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11309,11 +11141,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -11321,7 +11149,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11562,11 +11390,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -11574,7 +11398,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11815,11 +11639,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -11827,7 +11647,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12068,11 +11888,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -12080,7 +11896,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12321,11 +12137,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -12333,7 +12145,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12530,11 +12342,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -12542,7 +12350,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12783,11 +12591,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -12795,7 +12599,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13036,11 +12840,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -13048,7 +12848,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13289,11 +13089,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -13301,7 +13097,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13542,11 +13338,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -13554,7 +13346,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13795,11 +13587,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -13807,7 +13595,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14048,11 +13836,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -14060,7 +13844,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
